--- a/www/download/COUNTRY.ROW.rpO1.xlsx
+++ b/www/download/COUNTRY.ROW.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Resto do mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>856.406</t>
+          <t>2.19049719192514</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>877.09</t>
+          <t>2.10370921406971</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>896.559</t>
+          <t>2.03141108032851</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>911.591</t>
+          <t>2.01782559790231</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>926.097</t>
+          <t>2.12504178930266</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>955.308</t>
+          <t>2.02912786579775</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>983.772</t>
+          <t>1.96151944566172</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>998.606</t>
+          <t>2.02999091863113</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1035.462</t>
+          <t>2.27016540773809</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1066.542</t>
+          <t>2.0680500698185</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1095.297</t>
+          <t>2.09284450520906</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1124.55</t>
+          <t>2.03451754236666</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1146.413</t>
+          <t>1.98847752331369</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1174.341</t>
+          <t>1.9199923946533</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1192.928</t>
+          <t>1.89830444190864</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>370.557</t>
+          <t>3.86920809932848</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>379.509</t>
+          <t>3.72655579297538</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>390.19</t>
+          <t>3.61224381878103</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>395.691</t>
+          <t>3.59743873141907</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>400.131</t>
+          <t>3.75400641626665</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>413.204</t>
+          <t>3.67978638313392</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>426.421</t>
+          <t>3.5576138284824</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>433.848</t>
+          <t>3.63348150196631</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>450.765</t>
+          <t>3.87174222325787</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>467.784</t>
+          <t>3.64631395261499</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>483.061</t>
+          <t>3.69393707819979</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>500.543</t>
+          <t>3.60669563611433</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>514.72</t>
+          <t>3.51109966380433</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>530.955</t>
+          <t>3.39570435931419</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>3.34186545719055</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1581950.09</t>
+          <t>4.48427441194117</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1632216.323</t>
+          <t>4.35906153407907</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1661461.975</t>
+          <t>4.25290032701054</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1675206.949</t>
+          <t>4.27231196720371</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1699153.059</t>
+          <t>4.49267290563204</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1763177.932</t>
+          <t>4.43782451564672</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1837303.246</t>
+          <t>4.32353501067707</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1878897.895</t>
+          <t>4.41525768404414</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1972073.419</t>
+          <t>3.96006788287463</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2057200.705</t>
+          <t>4.4530397079433</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2101215.075</t>
+          <t>4.47153899794597</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2166673.727</t>
+          <t>4.35516878153266</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2217052.892</t>
+          <t>4.19555720282163</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2300250.74</t>
+          <t>4.0219939177866</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2339590.627</t>
+          <t>4.00187397388341</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>684490.338</t>
+          <t>122053113881417</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>706246.059</t>
+          <t>119009606317833</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>723082.616</t>
+          <t>123258518941476</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>727150.964</t>
+          <t>126650917708868</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>734138.16</t>
+          <t>139407474955530</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>762635.984</t>
+          <t>173909326333619</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>796388.724</t>
+          <t>182665087806477</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>816293.521</t>
+          <t>178874710383648</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>858497.817</t>
+          <t>194866676208319</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>902286.807</t>
+          <t>192269911771926</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>926704.183</t>
+          <t>207533588071386</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>964398.177</t>
+          <t>207661089271246</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>995418.423</t>
+          <t>181654716259591</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1040011.962</t>
+          <t>174108114170917</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1060308.098</t>
+          <t>150156272506233</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>29714370350604.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>28209024035722.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>29341949755958.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>31384107989470.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>33775003760457.3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>39989227533991.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>42647675979334.5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>40390027331860.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>42510137631383.6</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>40457688902638.5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>41373452884140.8</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>40384157621284</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>35182552757904.6</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>32138334713872.7</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>29158503962542</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>803216454.619827</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>728128630.641644</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>740879945.434698</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>811565922.437415</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>872687955.916447</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>1008281898.17397</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>1072026842.93598</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>1049710407.18017</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>993966357.685006</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>818221331.864372</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>727225087.357162</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>620430507.096749</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>456061292.654757</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>342319834.153307</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>330422254.324843</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>2549260.64462196</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>2785657.69799042</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>2835265.50343275</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>2668528.32312169</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>2769408.70234245</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>3110234.41560974</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>3058202.4638203</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>3114340.65030867</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>3556470.70058675</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>4293838.3812946</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>5176545.45398059</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>6080968.29112018</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>6996996.65430016</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>9151796.95523925</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>7889649.97721955</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>5487103.09086572</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>6009477.54139481</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>6093279.48065094</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>5681901.25606844</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>5829811.83114936</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>6412510.15369054</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>6368874.19585171</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>6520654.39186475</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>7463908.36111671</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>8851443.99394753</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>10694717.4121162</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>12413235.6924967</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>14480929.9608889</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>18491647.1669537</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>16603432.0870598</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>3.34948286612085</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>834359.584527764</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>875995.799515621</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.12</t>
+          <t>888232.735690991</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>817887.455920437</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>34.61</t>
+          <t>820870.645971099</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34.03</t>
+          <t>836667.08690153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>817433.866052652</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>808667.728954467</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>900867.030276919</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>1020802.53907012</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>1174139.92751623</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>1288849.39089663</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>1462975.42687985</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>1414733.6337512</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>1300131.74826274</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80188.4972281454</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74330.2729444097</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75199.095200447</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79314.6801937866</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84409.9444679262</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96778.3529935541</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100013.039624647</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93097.2779721899</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94306.6101615558</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86487.8952359105</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85648.4177042333</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80680.6219218503</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68352.8536751792</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60529.321563239</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53933.5345649332</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>-1275610030025.54</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.752</t>
+          <t>-1445560442408.23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>-3256515767540.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.711</t>
+          <t>-3017790271879.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>-3550034792888.46</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>-6222815105134.86</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>-4907560091864.87</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>-6870614494466.9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-7468682407799.58</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.269</t>
+          <t>-9975106725640.74</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.609</t>
+          <t>-13453423885245.9</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.975</t>
+          <t>-15739599094906.6</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3.462</t>
+          <t>-14361563416828.5</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-13848284272830.2</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>-7006913155342.68</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>3392200492757.14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>3099173879996.98</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>2529089211603.25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>3080704925341.06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>3124782548512.01</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>2663845210263.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>3489726425948.96</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.012</t>
+          <t>2841634978820.93</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>2767250187228.9</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>662231468733.289</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.963</t>
+          <t>-2388610909449.89</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>-4678960738129.12</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.944</t>
+          <t>-4689441425607.58</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.811</t>
+          <t>-6655596869343.06</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>-1430586427162.44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11.287</t>
+          <t>-4667810522782.68</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.943</t>
+          <t>-4544734322405.21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.946</t>
+          <t>-5785604979143.47</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11.365</t>
+          <t>-6098495197220.86</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11.408</t>
+          <t>-6674817341400.47</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11.324</t>
+          <t>-8886660315397.93</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.035</t>
+          <t>-8397286517813.83</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.701</t>
+          <t>-9712249473287.83</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11.762</t>
+          <t>-10235932595028.5</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13.123</t>
+          <t>-10637338194374</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.756</t>
+          <t>-11064812975796</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16.116</t>
+          <t>-11060638356777.5</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>18.165</t>
+          <t>-9672121991220.96</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>16.479</t>
+          <t>-7192687403487.12</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>-5576326728180.24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.003</t>
+          <t>359443.145731779</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.424</t>
+          <t>323298.248605797</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>318639.501803448</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6.264</t>
+          <t>334269.199150358</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.334</t>
+          <t>366940.987503922</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6.598</t>
+          <t>412465.094988843</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.586</t>
+          <t>414778.001120194</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>391579.435318226</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.373</t>
+          <t>407786.488679277</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>363138.517541494</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10.019</t>
+          <t>362050.682983217</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>11.506</t>
+          <t>334224.369548859</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>13.579</t>
+          <t>276863.179425286</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>16.651</t>
+          <t>239075.989648234</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>208541.102698242</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>181955.63222069</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>170388.05197782</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>176807.061535941</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.221</t>
+          <t>187784.247380756</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.257</t>
+          <t>202772.428008017</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.398</t>
+          <t>236602.194684312</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>245882.683215467</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>230013.87472595</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.736</t>
+          <t>236119.850597694</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>222103.469691237</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>222555.252845037</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>212998.252798287</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>6.786</t>
+          <t>183773.623428327</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>8.286</t>
+          <t>164155.341349108</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>7.707</t>
+          <t>147594.53968586</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>219.05</t>
+          <t>701304.802261108</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>210.37</t>
+          <t>776487.373711383</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>203.14</t>
+          <t>635985.074643795</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>201.78</t>
+          <t>643545.401190691</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>824736.144773895</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>202.91</t>
+          <t>1081819.67187864</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>196.15</t>
+          <t>1089314.484167</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1102602.17304957</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>227.02</t>
+          <t>1308815.13215068</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>206.81</t>
+          <t>1623206.21854965</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>209.28</t>
+          <t>2014786.55736804</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>203.45</t>
+          <t>2317531.5351085</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>198.85</t>
+          <t>2656330.43359939</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>3336283.80342492</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>189.83</t>
+          <t>2360037.21884672</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>386.92</t>
+          <t>20087884632917.9</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>372.66</t>
+          <t>20078544230350.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>361.22</t>
+          <t>16184943681037.8</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>359.74</t>
+          <t>18034326365434.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>375.4</t>
+          <t>26052515943290.4</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>367.98</t>
+          <t>41323876214494</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>355.76</t>
+          <t>43562051060269.2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>363.35</t>
+          <t>43970322458776.8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>387.17</t>
+          <t>49133297785333.1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>364.63</t>
+          <t>52214352604869.9</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>369.39</t>
+          <t>60210293937236.3</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>360.67</t>
+          <t>61706649027323.6</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>351.11</t>
+          <t>52593241114724.1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>339.57</t>
+          <t>50913270504366.5</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>334.19</t>
+          <t>32182484320207.1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>448.43</t>
+          <t>1058937.18147773</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>435.91</t>
+          <t>1116736.07292101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>425.29</t>
+          <t>1044258.26035641</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>427.23</t>
+          <t>1011695.46046075</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>449.27</t>
+          <t>1054009.48402831</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>443.78</t>
+          <t>1179943.33914034</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>432.35</t>
+          <t>1176102.18515089</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>441.53</t>
+          <t>1252329.84766961</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>396.01</t>
+          <t>1469427.2441954</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>445.3</t>
+          <t>1797530.83578138</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>447.15</t>
+          <t>2133448.93119307</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>435.52</t>
+          <t>2477531.07134706</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>419.56</t>
+          <t>3027613.30210319</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>402.2</t>
+          <t>3566779.2030106</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>400.19</t>
+          <t>2796920.48323512</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>155827970.989</t>
+          <t>31864763524354</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>149445606.057</t>
+          <t>29706307781025.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>158517949.465</t>
+          <t>26538475310862.4</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>171182455.505</t>
+          <t>28822643873519.1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>187786944.561</t>
+          <t>31759895763184</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>226028085.051</t>
+          <t>39566025640691.7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>241892513.244</t>
+          <t>42901231756592.5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>229693141.746</t>
+          <t>44163145822592.7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>244493186.339</t>
+          <t>48801666902292.8</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>236882589.93</t>
+          <t>48593292267645.9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>243764049.81</t>
+          <t>50601983171998.7</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>239527272.088</t>
+          <t>50387198878565</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>210680458.643</t>
+          <t>45783792533810.8</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>192774429.465</t>
+          <t>40530387546828.5</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>176069625.387</t>
+          <t>31638742804747.5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>133194000.654</t>
+          <t>-357632.379216618</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>122694666.713</t>
+          <t>-340248.699209626</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>124330009.919</t>
+          <t>-408273.185712613</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>132267325.772</t>
+          <t>-368150.059270054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>146824326.339</t>
+          <t>-229273.33925441</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>170432333.504</t>
+          <t>-98123.6672616966</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>176870114.752</t>
+          <t>-86787.7009838913</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>169885784.414</t>
+          <t>-149727.674620044</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>183815956.573</t>
+          <t>-160612.112044718</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>169870536.578</t>
+          <t>-174324.617231727</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>174892744.964</t>
+          <t>-118662.373825036</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>167293822.224</t>
+          <t>-159999.536238555</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>142506901.952</t>
+          <t>-371282.868503794</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>126938547.78</t>
+          <t>-230495.399585683</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>112745189.397</t>
+          <t>-436883.264388399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>122053113.881</t>
+          <t>-11776878891436.1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>119009606.318</t>
+          <t>-9627763550675.22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>123258518.941</t>
+          <t>-10353531629824.6</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>126650917.709</t>
+          <t>-10788317508084.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>139407474.956</t>
+          <t>-5707379819893.61</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>173909326.334</t>
+          <t>1757850573802.33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>182665087.806</t>
+          <t>660819303676.66</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>178874710.384</t>
+          <t>-192823363815.943</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>194866676.208</t>
+          <t>331630883040.31</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>192269911.772</t>
+          <t>3621060337223.98</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>207533588.071</t>
+          <t>9608310765237.6</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>207661089.271</t>
+          <t>11319450148758.6</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>181654716.26</t>
+          <t>6809448580913.27</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>174108114.171</t>
+          <t>10382882957538</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>150156272.506</t>
+          <t>543741515459.596</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5.487</t>
+          <t>1693452.24787689</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6.009</t>
+          <t>1815616.36512757</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6.093</t>
+          <t>1835440.60484036</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5.682</t>
+          <t>1710026.40859875</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>1753515.4220765</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6.413</t>
+          <t>1895478.1988017</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6.369</t>
+          <t>1856320.04175743</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6.521</t>
+          <t>1874128.27508539</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>7.464</t>
+          <t>2096782.94164291</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8.851</t>
+          <t>2481700.42397383</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10.695</t>
+          <t>2938719.14606415</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>12.413</t>
+          <t>3403204.25777267</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>14.481</t>
+          <t>3942426.48415527</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>18.492</t>
+          <t>4952165.09986518</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>16.603</t>
+          <t>4395050.71325839</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>56704821.218</t>
+          <t>-0.0739203932753493</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>55166197.675</t>
+          <t>-0.0733510692176721</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>57353454.387</t>
+          <t>-0.0743544942777961</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>59482125.054</t>
+          <t>-0.0719684915091149</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>66224482.967</t>
+          <t>-0.0719576120389443</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>84350552.123</t>
+          <t>-0.0738822163236586</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>87712020.116</t>
+          <t>-0.0740785675068383</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>85432649.606</t>
+          <t>-0.0755670600218539</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>92851839.938</t>
+          <t>-0.0765913131631231</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>93270197.19</t>
+          <t>-0.0777855322760167</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>100452121.405</t>
+          <t>-0.0795722985676879</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>101728552.526</t>
+          <t>-0.0799720171145983</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>87773191.731</t>
+          <t>-0.0805374597281697</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>86168749.315</t>
+          <t>-0.0858503760875483</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>71351538.992</t>
+          <t>-0.0830100473911866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>1656099.77634291</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.786</t>
+          <t>1752367.9646248</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.835</t>
+          <t>1775560.24831936</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>1710628.53985104</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.769</t>
+          <t>1729179.1735902</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1808311.6142287</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.058</t>
+          <t>1805400.01718355</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3.114</t>
+          <t>1776618.243776</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>3.556</t>
+          <t>1970113.47623266</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4.294</t>
+          <t>2268914.53320351</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>5.177</t>
+          <t>2608844.29810359</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6.081</t>
+          <t>2975171.26753475</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>6.997</t>
+          <t>3462290.42564073</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>9.152</t>
+          <t>4230212.3731713</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>3950317.57228416</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>29714370.351</t>
+          <t>1912553.25961093</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>28209024.036</t>
+          <t>2024580.61430081</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29341949.756</t>
+          <t>2042561.38369465</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31384107.989</t>
+          <t>1955571.25946932</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>33775003.76</t>
+          <t>1972638.68944014</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>39989227.534</t>
+          <t>2051263.03792785</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>42647675.979</t>
+          <t>2042383.82250289</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>40390027.332</t>
+          <t>2011676.3093988</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>42510137.631</t>
+          <t>2240887.68697854</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>40457688.903</t>
+          <t>2581201.91080858</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>41373452.884</t>
+          <t>2963357.73251987</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>40384157.621</t>
+          <t>3375554.56705043</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>35182552.758</t>
+          <t>3944366.02144599</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>32138334.714</t>
+          <t>4810828.23995541</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>29158503.963</t>
+          <t>4486795.96693829</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>11287271.9902858</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>11942508.9348878</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>11945918.5933329</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>11364521.3171774</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>11407697.1526909</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>11324336.6067459</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>11034687.812736</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>10701325.7988415</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>11762000.0633527</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>13123295.6721036</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>14755636.6807407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>16116254.6275372</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>18165154.8461758</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>16479061.5746225</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>15662341.9588696</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>803.216</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>728.129</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>740.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>811.566</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>872.688</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1008.282</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1072.027</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1049.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>993.966</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>818.221</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>727.225</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>620.431</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>456.061</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>342.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>330.422</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>133194000654146</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>122694666713368</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>124330009919118</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>132267325771937</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>146824326338943</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>170432333503721</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>176870114752224</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>169885784413828</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>183815956572696</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>169870536578383</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>174892744963539</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>167293822224243</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>142506901952339</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>126938547780316</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>112745189397121</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>155827970988504</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>149445606057324</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>158517949465089</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>171182455505399</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>187786944560748</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>226028085050633</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>241892513244266</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>229693141745934</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>244493186338795</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>236882589930044</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>243764049810257</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>239527272087600</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>210680458642506</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>192774429464613</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>176069625386819</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>56704821217850.9</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>55166197675336.5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>57353454386708.4</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>59482125053564.5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>66224482967114</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>84350552123029</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>87712020116141.5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>85432649605690.1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>92851839937638.7</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>93270197190304.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>100452121405482</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>101728552525690</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>87773191731408.8</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>86168749315064.2</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>71351538991837.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>856406416.7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>877089703.9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>896558927.5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>911591136.6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>926097036</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>955308488.8</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>983772057.8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>998605592.9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1035462227</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1066541600</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1095296771</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1124550408</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1146412933</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1174341498</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1192927772</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>370556518.425133</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>379509221.724772</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>390190196.806831</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>395691036.171245</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>400130624.103076</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>413204257.946556</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>426421156.075177</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>433847564.736811</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>450765196.188898</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>467784408.353138</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>483061497.143057</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>500543459.622823</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>514719589.10591</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>530954814.689202</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>540637734.903813</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1581950090380.27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1632216323446.71</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1661461975045.46</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1675206949481.46</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1699153059439.56</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1763177932464.47</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1837303245908.48</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1878897894530.26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1972073419433.81</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2057200705221.21</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2101215074715.22</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2166673727183.3</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2217052892146.03</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2300250740267.96</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2339590626746.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>684490338211.679</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>706246058804.897</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>723082616373.875</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>727150963878.283</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>734138160140.059</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>762635983824.331</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>796388724368.756</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>816293521413.016</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>858497817332.735</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>902286806961.455</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>926704183455.952</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>964398176874.085</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>995418422823.631</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1040011962123.2</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1060308098055.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228898648427933</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.231919837016752</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.233019160662987</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.235284951021892</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.240991356161571</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.247797250380012</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.249827856813299</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.256671032957441</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.249986894033455</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.274989880290778</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.282125256882255</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.287263989153529</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289429468407217</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.297021226523762</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.306401074424642</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.453619150842876</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.458991502302581</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.463130386661843</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.465589634981445</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.471018569897122</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.471636483388593</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.473224520750676</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.47349384372661</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.460707877633889</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472300993256089</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.470266756125835</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.469502423185547</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466965109699573</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.464136590079048</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.463349681517467</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.317482200729191</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.309088660680667</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.30385045267517</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.299125413996663</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.287990073941307</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.280566266231395</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.276947622436025</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.269835123315949</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.289305228332656</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.252709126453133</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.24760798699191</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.243233587660924</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.24360542189321</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.23884218339719</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.230249244057891</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.155282646906169</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.157701180745512</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.159117651873489</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.160829657779038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.164682133111337</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.168121531150933</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.170713780599449</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176732786541879</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.182257267892264</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.191332324721546</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.196486156235948</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.200505416481349</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.204207737261477</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.210861564497349</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.219257860870625</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.469773565988899</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.475494398270178</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.479710527481293</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.482224189295601</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.489192905849045</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.491557547666794</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.49292446743076</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.494602048512791</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.496828174229481</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.4980998533911</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.498983843039248</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.499095031787207</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.496367579988465</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.49598976431317</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.496499581531323</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.374943787104932</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.36680442098431</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.361171820645218</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.356946152925361</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.346124961039618</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.340320921182273</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.336361751969791</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.32866516494533</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.320914557878256</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.310567821887355</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.304530000724804</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.300399551731444</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.299424682750058</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.293148671189482</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.284242557598052</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6003296.72858969</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6424492.30466808</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6543783.60858558</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6264479.68287485</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>6333545.30128171</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6598368.92172176</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6585685.88599394</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>6543553.25004621</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7373150.32141448</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8620444.58875593</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10018945.050815</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>11505716.776729</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>13579035.7644158</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>16651487.3993075</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15730361.8590702</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3100061.91984787</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3310373.4744688</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3370415.8176897</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3221261.55108232</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3257066.93491647</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3398413.01767922</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3375819.90928846</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3352394.52778614</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>3736360.3239901</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4357033.25331906</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5050013.08052761</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5791309.48199016</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6786121.13592133</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>8285953.90396788</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7706866.58207004</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
